--- a/planilhas/LISTA DE PROCESSO PDG POWERADE.xlsx
+++ b/planilhas/LISTA DE PROCESSO PDG POWERADE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\PROJETOS -BACKEND\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\PROJETOS EM ANDAMENTO\PAINEL DE CONTROLE MTECH\PROGRAMAS\PROJETOS -BACKEND\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BF85DF-0C44-4665-AEE3-B9142A157AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF9545F-B729-4401-8D74-F92904A338DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{017E89C7-FFDB-48B6-A349-28129EB10CCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{017E89C7-FFDB-48B6-A349-28129EB10CCE}"/>
   </bookViews>
   <sheets>
     <sheet name="PDG POWERADE" sheetId="1" r:id="rId1"/>
@@ -1763,7 +1763,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1922,8 +1922,12 @@
       <c r="F56">
         <v>125</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I56">
+        <f>125*E58</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1943,7 +1947,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>4</v>
       </c>
@@ -1964,7 +1968,7 @@
       </c>
       <c r="G58"/>
     </row>
-    <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>4</v>
       </c>
@@ -1985,7 +1989,7 @@
       </c>
       <c r="G59"/>
     </row>
-    <row r="60" spans="1:7" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>4</v>
       </c>
@@ -2006,7 +2010,7 @@
       </c>
       <c r="G60"/>
     </row>
-    <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>4</v>
       </c>
@@ -2027,7 +2031,7 @@
       </c>
       <c r="G61"/>
     </row>
-    <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>4</v>
       </c>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="G62"/>
     </row>
-    <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>4</v>
       </c>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="G63"/>
     </row>
-    <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>4</v>
       </c>
